--- a/Assets/Data/Excel/ItemTable.xlsx
+++ b/Assets/Data/Excel/ItemTable.xlsx
@@ -7,39 +7,242 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ItemTable" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ItemTable" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
+  <si>
+    <t>uniqueId</t>
+  </si>
+  <si>
+    <t>itemId</t>
+  </si>
+  <si>
+    <t>itemName</t>
+  </si>
+  <si>
+    <t>itemType</t>
+  </si>
+  <si>
+    <t>effectValue</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>iconPath</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>weapon_sword_01</t>
+  </si>
+  <si>
+    <t>낡은 검</t>
+  </si>
+  <si>
+    <t>Equipment</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>오래된 검이지만 쓸만하다</t>
+  </si>
+  <si>
+    <t>Icons/weapon_sword_01</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>weapon_sword_02</t>
+  </si>
+  <si>
+    <t>강철 검</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>단단한 강철로 만든 검</t>
+  </si>
+  <si>
+    <t>Icons/weapon_sword_02</t>
+  </si>
+  <si>
+    <t>weapon_sword_03</t>
+  </si>
+  <si>
+    <t>마법 검</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>마력이 깃든 검</t>
+  </si>
+  <si>
+    <t>Icons/weapon_sword_03</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>potion_hp_small</t>
+  </si>
+  <si>
+    <t>작은 HP 포션</t>
+  </si>
+  <si>
+    <t>Consumable</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>HP를 20 회복한다</t>
+  </si>
+  <si>
+    <t>Icons/potion_hp_small</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>potion_hp_medium</t>
+  </si>
+  <si>
+    <t>중간 HP 포션</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>HP를 50 회복한다</t>
+  </si>
+  <si>
+    <t>Icons/potion_hp_medium</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>potion_hp_large</t>
+  </si>
+  <si>
+    <t>큰 HP 포션</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>HP를 100 회복한다</t>
+  </si>
+  <si>
+    <t>Icons/potion_hp_large</t>
+  </si>
+  <si>
+    <t>armor_leather</t>
+  </si>
+  <si>
+    <t>가죽 갑옷</t>
+  </si>
+  <si>
+    <t>가벼운 가죽 갑옷</t>
+  </si>
+  <si>
+    <t>Icons/armor_leather</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>armor_iron</t>
+  </si>
+  <si>
+    <t>쇠 갑옷</t>
+  </si>
+  <si>
+    <t>단단한 쇠로 만든 갑옷</t>
+  </si>
+  <si>
+    <t>Icons/armor_iron</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>ring_magic</t>
+  </si>
+  <si>
+    <t>마력 반지</t>
+  </si>
+  <si>
+    <t>마력을 높여주는 반지</t>
+  </si>
+  <si>
+    <t>Icons/ring_magic</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>potion_antidote</t>
+  </si>
+  <si>
+    <t>해독제</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>독 상태를 해제한다</t>
+  </si>
+  <si>
+    <t>Icons/potion_antidote</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>potion_stamina</t>
+  </si>
+  <si>
+    <t>강화 물약</t>
+  </si>
+  <si>
+    <t>잠시 공격력이 올라간다</t>
+  </si>
+  <si>
+    <t>Icons/potion_stamina</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -54,14 +257,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
+  <cellXfs count="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -424,254 +624,287 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>uniqueId</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>itemId</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>itemName</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>itemType</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>effectValue</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>iconPath</t>
-        </is>
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>weapon_sword_01</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>낡은 검</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Equipment</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>오래된 검이지만 쓸만하다</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Icons/weapon_sword_01</t>
-        </is>
+      <c r="A2" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>weapon_sword_02</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>강철 검</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Equipment</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>단단한 강철로 만든 검</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>7</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Icons/weapon_sword_02</t>
-        </is>
+      <c r="A3" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="0" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>weapon_sword_03</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>마법 검</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Equipment</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>마력이 깃든 검</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>12</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Icons/weapon_sword_03</t>
-        </is>
+      <c r="A4" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="0" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>potion_hp_small</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>작은 HP 포션</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Consumable</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>HP를 20 회복한다</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>20</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Icons/potion_hp_small</t>
-        </is>
+      <c r="A5" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" s="0" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>potion_hp_medium</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>중간 HP 포션</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Consumable</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>HP를 50 회복한다</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
+      <c r="A6" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="G6" s="0" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" s="0" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="G8" s="0" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Icons/potion_hp_medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>potion_hp_large</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>큰 HP 포션</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Consumable</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>HP를 100 회복한다</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>100</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Icons/potion_hp_large</t>
-        </is>
+      <c r="D9" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="G9" s="0" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="G10" s="0" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="D11" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="F11" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="G11" s="0" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="D12" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="F12" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="G12" s="0" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>